--- a/aysha/FittingTests.xlsx
+++ b/aysha/FittingTests.xlsx
@@ -1,31 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6AF479-A372-48EC-A6DA-56BB467FC295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D4B5AC-AB60-4A36-B381-850C8AC2677E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="0D" sheetId="1" r:id="rId1"/>
+    <sheet name="3D" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="87">
   <si>
     <t>A</t>
   </si>
@@ -118,6 +131,174 @@
   </si>
   <si>
     <t>no convergence</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>as close as possible to E67</t>
+  </si>
+  <si>
+    <t>v7</t>
+  </si>
+  <si>
+    <t>conjugated</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>temperature appeared too low</t>
+  </si>
+  <si>
+    <t>Raytracing</t>
+  </si>
+  <si>
+    <t>changed power x8 to achieve Power on apperture equal to all other cases</t>
+  </si>
+  <si>
+    <t>profile improved significantly but too high</t>
+  </si>
+  <si>
+    <t>power x4 incase the 1/4 symmetry creates the issues</t>
+  </si>
+  <si>
+    <t>agreement got better not ideal</t>
+  </si>
+  <si>
+    <t>no correction as original E67 without the 0.64</t>
+  </si>
+  <si>
+    <t>Heat</t>
+  </si>
+  <si>
+    <t>Cps x 4</t>
+  </si>
+  <si>
+    <t>too low</t>
+  </si>
+  <si>
+    <t>too high</t>
+  </si>
+  <si>
+    <t>added 4x on Psrc</t>
+  </si>
+  <si>
+    <t>back to Cps</t>
+  </si>
+  <si>
+    <t>repeated x4 on Psrc and 0.64 on Io</t>
+  </si>
+  <si>
+    <t>again to high</t>
+  </si>
+  <si>
+    <t>changed to x2</t>
+  </si>
+  <si>
+    <t>removed 0.64, and changed h_nat=10</t>
+  </si>
+  <si>
+    <t>corrected V0 to qlpm/4 to account for 1/4 symmetry</t>
+  </si>
+  <si>
+    <t>added 0.64, h_nat=1, and 1.87x Psrc to match total absorbed power</t>
+  </si>
+  <si>
+    <t>promising results, T3 very good time series, T-length not bad, pasted pictures to Aysha</t>
+  </si>
+  <si>
+    <t>overal temperature reduced, and profile didn’t get better</t>
+  </si>
+  <si>
+    <t>initial of 3b, 1 min</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>broadening C limit didn't help</t>
+  </si>
+  <si>
+    <t>C limit to 30</t>
+  </si>
+  <si>
+    <t>corrected m(qlpm, Tamb) and G flux in Re</t>
+  </si>
+  <si>
+    <t>2. x Psrc</t>
+  </si>
+  <si>
+    <t>not bad, but solid not great, modeled is higher, also very strange behavior for Nu because of Pr</t>
+  </si>
+  <si>
+    <t>changed Pr expressin to fixed Tamb</t>
+  </si>
+  <si>
+    <t>gas slightly lower, solid slight higher</t>
+  </si>
+  <si>
+    <t>gas all lower, gas better but all slightly higher</t>
+  </si>
+  <si>
+    <t>similar</t>
+  </si>
+  <si>
+    <t>Cp</t>
+  </si>
+  <si>
+    <t>scatter plot ok but solid profiles not</t>
+  </si>
+  <si>
+    <t>scatter plot worse and solid profiles not</t>
+  </si>
+  <si>
+    <t>gas scatter and profiles ok, solid not</t>
+  </si>
+  <si>
+    <t>solid profiles better than gas</t>
+  </si>
+  <si>
+    <t>init #26, changed limits of A B C</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>change limits for C</t>
+  </si>
+  <si>
+    <t>reworked some of the inputs to be able for non-isothermal flow; poor</t>
+  </si>
+  <si>
+    <t>T9-T10</t>
+  </si>
+  <si>
+    <t>had trouble to repeat #9, deactivated multi-physics for surface radiation</t>
+  </si>
+  <si>
+    <t>same as #9, w 2xPsrc</t>
+  </si>
+  <si>
+    <t>too high temperature</t>
+  </si>
+  <si>
+    <t>1.6Psrc</t>
+  </si>
+  <si>
+    <t>gave a good agreement on the Length Profilel</t>
+  </si>
+  <si>
+    <t>1.4x</t>
+  </si>
+  <si>
+    <t>hnat=10</t>
+  </si>
+  <si>
+    <t>better match but not at all points</t>
+  </si>
+  <si>
+    <t>try to change the front temperature</t>
   </si>
 </sst>
 </file>
@@ -125,7 +306,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -165,13 +346,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,13 +636,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:M14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:O37"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="13" max="13" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="46.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -490,13 +674,19 @@
         <v>27</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -531,13 +721,19 @@
         <v>28</v>
       </c>
       <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0.4</v>
+      </c>
+      <c r="N3">
         <v>499.47699999999998</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -553,14 +749,14 @@
       <c r="E4">
         <v>0.66</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>528.26599999999996</v>
       </c>
-      <c r="M4" t="s">
+      <c r="O4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -579,14 +775,14 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>473.34</v>
       </c>
-      <c r="M5" t="s">
+      <c r="O5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -602,11 +798,11 @@
       <c r="G6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M6" t="s">
+      <c r="O6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -622,14 +818,14 @@
       <c r="G7">
         <v>1</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>604.08600000000001</v>
       </c>
-      <c r="M7" t="s">
+      <c r="O7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -645,11 +841,11 @@
       <c r="E8">
         <v>0.7</v>
       </c>
-      <c r="M8" t="s">
+      <c r="O8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -665,11 +861,11 @@
       <c r="E9">
         <v>0.63</v>
       </c>
-      <c r="M9" t="s">
+      <c r="O9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -685,14 +881,14 @@
       <c r="G10">
         <v>1.2</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>500</v>
       </c>
-      <c r="M10" t="s">
+      <c r="O10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -708,14 +904,17 @@
       <c r="E11">
         <v>0.64</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>480</v>
       </c>
-      <c r="M11" t="s">
+      <c r="O11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>9</v>
+      </c>
       <c r="B12" s="2">
         <v>2.6620817681730501E-5</v>
       </c>
@@ -728,30 +927,669 @@
       <c r="I12" t="s">
         <v>21</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>672</v>
       </c>
-      <c r="M12" t="s">
+      <c r="O12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>10</v>
+      </c>
       <c r="J13" t="s">
         <v>25</v>
       </c>
-      <c r="M13" t="s">
+      <c r="O13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>11</v>
+      </c>
       <c r="K14" t="s">
         <v>29</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>25612</v>
       </c>
-      <c r="M14" t="s">
+      <c r="O14" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3.3035945380220997E-5</v>
+      </c>
+      <c r="C15">
+        <v>1.43770025274668</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="J15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N15">
+        <v>469</v>
+      </c>
+      <c r="O15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="N16" t="s">
+        <v>58</v>
+      </c>
+      <c r="O16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1.03191509408719E-5</v>
+      </c>
+      <c r="C17">
+        <v>1.4319313285872399</v>
+      </c>
+      <c r="D17">
+        <v>25.984272299692599</v>
+      </c>
+      <c r="N17">
+        <v>465</v>
+      </c>
+      <c r="O17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="O18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="E19">
+        <v>0.84</v>
+      </c>
+      <c r="N19">
+        <v>850</v>
+      </c>
+      <c r="O19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="O20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="E21">
+        <v>0.74</v>
+      </c>
+      <c r="F21">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N21">
+        <v>573</v>
+      </c>
+      <c r="O21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="E22">
+        <v>0.64</v>
+      </c>
+      <c r="N22">
+        <v>607</v>
+      </c>
+      <c r="O22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23">
+        <v>5.6058995390906102E-4</v>
+      </c>
+      <c r="C23">
+        <v>1.6106589591624401</v>
+      </c>
+      <c r="D23">
+        <v>9.910468968988089E-4</v>
+      </c>
+      <c r="E23">
+        <v>0.7</v>
+      </c>
+      <c r="N23">
+        <v>502</v>
+      </c>
+      <c r="O23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1.0024299213338499E-5</v>
+      </c>
+      <c r="C24">
+        <v>2.9323882617891202</v>
+      </c>
+      <c r="D24">
+        <v>1E-4</v>
+      </c>
+      <c r="L24">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="N24">
+        <v>1641</v>
+      </c>
+      <c r="O24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" s="2">
+        <v>2.0887059774144901E-5</v>
+      </c>
+      <c r="C25">
+        <v>2.5052539496126101</v>
+      </c>
+      <c r="D25">
+        <v>1.8829968719792201E-2</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>1071</v>
+      </c>
+      <c r="O25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>1892</v>
+      </c>
+      <c r="O26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27">
+        <v>2.1591196456141501E-4</v>
+      </c>
+      <c r="C27">
+        <v>1.7189995203791599</v>
+      </c>
+      <c r="D27">
+        <v>1.20209817420813</v>
+      </c>
+      <c r="E27">
+        <v>0.9</v>
+      </c>
+      <c r="N27">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28">
+        <v>3.0880065502844102E-4</v>
+      </c>
+      <c r="C28">
+        <v>1.7074022707650001</v>
+      </c>
+      <c r="D28">
+        <v>3.7186641941726502E-4</v>
+      </c>
+      <c r="E28">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="E29">
+        <v>0.7</v>
+      </c>
+      <c r="N29">
+        <v>502</v>
+      </c>
+      <c r="O29" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>4.60311808037377E-4</v>
+      </c>
+      <c r="C30">
+        <v>1.66187478217667</v>
+      </c>
+      <c r="D30">
+        <v>1.3738648256894E-4</v>
+      </c>
+      <c r="N30">
+        <v>502</v>
+      </c>
+      <c r="O30" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>5.86247778425387E-4</v>
+      </c>
+      <c r="C31">
+        <v>1.6630696101604501</v>
+      </c>
+      <c r="D31" s="2">
+        <v>9.39537377217747E-5</v>
+      </c>
+      <c r="M31">
+        <v>0.6</v>
+      </c>
+      <c r="N31">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="N32">
+        <v>522</v>
+      </c>
+      <c r="O32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33">
+        <v>2.8727643386340098E-4</v>
+      </c>
+      <c r="C33">
+        <v>1.5904189645704501</v>
+      </c>
+      <c r="D33">
+        <v>1.0263197679569199E-4</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B34">
+        <v>3.0928717643758302E-4</v>
+      </c>
+      <c r="C34">
+        <v>1.5965904733758101</v>
+      </c>
+      <c r="D34">
+        <v>2.4080124471630401E-4</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N34">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B35">
+        <v>2.4681495887314401E-4</v>
+      </c>
+      <c r="C35">
+        <v>1.6624759537039799</v>
+      </c>
+      <c r="D35">
+        <v>1.7341179006468701E-4</v>
+      </c>
+      <c r="K35" t="s">
+        <v>77</v>
+      </c>
+      <c r="N35">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E36">
+        <v>0.64</v>
+      </c>
+      <c r="K36" t="s">
+        <v>28</v>
+      </c>
+      <c r="N36">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E37">
+        <v>0.75</v>
+      </c>
+      <c r="N37">
+        <v>550</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5B19FA9-A01B-4042-9995-5A31C36523E9}">
+  <dimension ref="A2:G25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="9.109375" style="4"/>
+    <col min="3" max="3" width="31.88671875" style="4" customWidth="1"/>
+    <col min="4" max="6" width="33.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>4</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>12</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>13</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>14</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>15</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>16</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>17</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/aysha/FittingTests.xlsx
+++ b/aysha/FittingTests.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\tamuq-chen-secarelab-receiver\aysha\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\transp02\d$\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D4B5AC-AB60-4A36-B381-850C8AC2677E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BC73FE-D035-4640-9039-D2CA19D5ADD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="3D" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="150">
   <si>
     <t>A</t>
   </si>
@@ -142,9 +141,6 @@
     <t>v7</t>
   </si>
   <si>
-    <t>conjugated</t>
-  </si>
-  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -298,7 +294,199 @@
     <t>better match but not at all points</t>
   </si>
   <si>
-    <t>try to change the front temperature</t>
+    <t>try to change the front temperature; not much difference</t>
+  </si>
+  <si>
+    <t>changed to E68</t>
+  </si>
+  <si>
+    <t>agreement seems similar, but still with the 1.4x in radiation, gas temperature is higher, although solid's looks ok</t>
+  </si>
+  <si>
+    <t>no factors, just the 0.8 correction</t>
+  </si>
+  <si>
+    <t>changed to E78 because of good 0D agreement</t>
+  </si>
+  <si>
+    <t>conjugated; one-way</t>
+  </si>
+  <si>
+    <t>transient solid is low, gas may end up good but not the solid</t>
+  </si>
+  <si>
+    <t>activated multiphysics surface radiation</t>
+  </si>
+  <si>
+    <t>deactivated</t>
+  </si>
+  <si>
+    <t>Surface - Surface Radiation</t>
+  </si>
+  <si>
+    <t>not working</t>
+  </si>
+  <si>
+    <t>added irradiance from ray tracing</t>
+  </si>
+  <si>
+    <t>not working, making a sorter test</t>
+  </si>
+  <si>
+    <t>enabled diffuse irradiance from Raytracing, but closed heat transfer source</t>
+  </si>
+  <si>
+    <t>lower temperature but works</t>
+  </si>
+  <si>
+    <t>deactivated multiphysics surface-surface radiation and readded raytracing source to heat-transfer</t>
+  </si>
+  <si>
+    <t>deactivated surface-surface radiation and multiphysics</t>
+  </si>
+  <si>
+    <t>not working as expected, there is a final result but not a printout during the solution; had to change the plotting units</t>
+  </si>
+  <si>
+    <t>gas temperature very good, not for the solid</t>
+  </si>
+  <si>
+    <t>re-enabled surface-surface radiation</t>
+  </si>
+  <si>
+    <t>no difference in the results</t>
+  </si>
+  <si>
+    <t>repeated #22</t>
+  </si>
+  <si>
+    <t>slower and significantly lower temperatures, continue without surface-surface radiation</t>
+  </si>
+  <si>
+    <t>x2 k_SiC</t>
+  </si>
+  <si>
+    <t>x1 k_SiC ; 4.4 * Cps</t>
+  </si>
+  <si>
+    <t>back to 1; hnat=1</t>
+  </si>
+  <si>
+    <t>added surface to ambient radiation</t>
+  </si>
+  <si>
+    <t>k insulation 0.05</t>
+  </si>
+  <si>
+    <t>seems to have a big impact</t>
+  </si>
+  <si>
+    <t>removed 0.8 from IoC</t>
+  </si>
+  <si>
+    <t>k insulation 0.078</t>
+  </si>
+  <si>
+    <t>k insulation 0.01</t>
+  </si>
+  <si>
+    <t>various tests, added average exit Tg</t>
+  </si>
+  <si>
+    <t>absorbtivity 0.8</t>
+  </si>
+  <si>
+    <t>gas is almost ok, the rest are high</t>
+  </si>
+  <si>
+    <t>7.1 created a model with insulation</t>
+  </si>
+  <si>
+    <t>7.2 extended the insulation to cover the back side</t>
+  </si>
+  <si>
+    <t>absorbtivity 0.7</t>
+  </si>
+  <si>
+    <t>results are to the same scale, but not capturing the x profile; nor the higher middle temperature</t>
+  </si>
+  <si>
+    <t>absorbtivity 0.75</t>
+  </si>
+  <si>
+    <t>included separate emissivity for insulation; h_nat=20</t>
+  </si>
+  <si>
+    <t>somehow similar to previous</t>
+  </si>
+  <si>
+    <t>increase RH to 0.3 from 0.2</t>
+  </si>
+  <si>
+    <t>T3 follows T10 closer</t>
+  </si>
+  <si>
+    <t>was hardcoded in Cp_air, changed to parameter and RH= 0.2</t>
+  </si>
+  <si>
+    <t>temperatures increased faster, and higher</t>
+  </si>
+  <si>
+    <t>RH=0.6</t>
+  </si>
+  <si>
+    <t>gives good agreement with E67 and E78 after modifying some properties and IoA, missing the temperature in the middle</t>
+  </si>
+  <si>
+    <t>increase the insulation size, and remove the T2 temperature</t>
+  </si>
+  <si>
+    <t>check for finer mesh in solid</t>
+  </si>
+  <si>
+    <t>changed kins to previous 0.078</t>
+  </si>
+  <si>
+    <t>overshoots temperature</t>
+  </si>
+  <si>
+    <t>good aggreement; missing temperature in the middle</t>
+  </si>
+  <si>
+    <t>refined solid mesh to obtain a representative</t>
+  </si>
+  <si>
+    <t>doesn't change the overall picture although it adds some strange "variation" in the solid thermocouples</t>
+  </si>
+  <si>
+    <t>refined more specifically the solid</t>
+  </si>
+  <si>
+    <t>changes the profile drastically!!! Verify</t>
+  </si>
+  <si>
+    <t>reduce IoA to normal</t>
+  </si>
+  <si>
+    <t>quite slow but seems ok</t>
+  </si>
+  <si>
+    <t>temperatures a bit lower than expected</t>
+  </si>
+  <si>
+    <t>refine 2: 11M elements</t>
+  </si>
+  <si>
+    <t>changed the mesh to something more reasonable 1.7M elements</t>
+  </si>
+  <si>
+    <t>activate surface-surface-radiation</t>
+  </si>
+  <si>
+    <t>temperature has strange profiles; although values appear reasonable</t>
+  </si>
+  <si>
+    <t>remove insulation, replace with flux</t>
   </si>
 </sst>
 </file>
@@ -326,12 +514,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -346,7 +540,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -354,6 +548,9 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -637,12 +834,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:O37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="15" max="15" width="46.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="46.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -674,10 +871,10 @@
         <v>27</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>7</v>
@@ -686,7 +883,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -733,7 +930,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -756,7 +953,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -782,7 +979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -802,7 +999,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -825,7 +1022,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -845,7 +1042,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -865,7 +1062,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -888,7 +1085,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -911,7 +1108,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -934,7 +1131,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -945,7 +1142,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -959,7 +1156,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -982,21 +1179,21 @@
         <v>469</v>
       </c>
       <c r="O15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="N16" t="s">
+        <v>57</v>
+      </c>
+      <c r="O16" t="s">
         <v>58</v>
       </c>
-      <c r="O16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1013,18 +1210,18 @@
         <v>465</v>
       </c>
       <c r="O17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="O18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1035,18 +1232,18 @@
         <v>850</v>
       </c>
       <c r="O19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="O20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1060,10 +1257,10 @@
         <v>573</v>
       </c>
       <c r="O21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1074,10 +1271,10 @@
         <v>607</v>
       </c>
       <c r="O22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1097,10 +1294,10 @@
         <v>502</v>
       </c>
       <c r="O23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -1120,10 +1317,10 @@
         <v>1641</v>
       </c>
       <c r="O24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -1143,10 +1340,10 @@
         <v>1071</v>
       </c>
       <c r="O25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -1157,10 +1354,10 @@
         <v>1892</v>
       </c>
       <c r="O26" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -1180,7 +1377,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -1197,7 +1394,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -1208,10 +1405,10 @@
         <v>502</v>
       </c>
       <c r="O29" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -1228,10 +1425,10 @@
         <v>502</v>
       </c>
       <c r="O30" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -1251,7 +1448,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -1259,10 +1456,10 @@
         <v>522</v>
       </c>
       <c r="O32" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -1282,7 +1479,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>3.0928717643758302E-4</v>
       </c>
@@ -1302,7 +1499,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B35">
         <v>2.4681495887314401E-4</v>
       </c>
@@ -1313,13 +1510,13 @@
         <v>1.7341179006468701E-4</v>
       </c>
       <c r="K35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N35">
         <v>482</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E36">
         <v>0.64</v>
       </c>
@@ -1330,7 +1527,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E37">
         <v>0.75</v>
       </c>
@@ -1345,31 +1542,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5B19FA9-A01B-4042-9995-5A31C36523E9}">
-  <dimension ref="A2:G25"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:I150"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.109375" style="4"/>
-    <col min="3" max="3" width="31.88671875" style="4" customWidth="1"/>
-    <col min="4" max="6" width="33.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="4"/>
+    <col min="1" max="2" width="9.140625" style="4"/>
+    <col min="3" max="3" width="31.85546875" style="4" customWidth="1"/>
+    <col min="4" max="7" width="33.28515625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="55.140625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="29.85546875" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -1377,219 +1578,1039 @@
         <v>33</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H3" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>4</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="G7" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>6</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="G9" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>8</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G10" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>9</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>10</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>11</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>12</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="G14" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>13</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>14</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>15</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>16</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="G18" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>17</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D20" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D21" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F22" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F23" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F24" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>23</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>24</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>25</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>26</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>27</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>28</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>29</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>30</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>31</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>32</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>33</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>34</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <v>35</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <v>36</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>37</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>38</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>39</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <v>40</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>41</v>
+      </c>
+      <c r="D43" s="5">
+        <v>7.2</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <v>42</v>
+      </c>
+      <c r="D44" s="4">
+        <v>7.3</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <v>43</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <v>44</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <v>45</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <v>46</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>47</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
+        <v>48</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="4">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="4">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="4">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="4">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="4">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="4">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="4">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="4">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="4">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="4">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="4">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="4">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="4">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="4">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="4">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="4">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="4">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="4">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="4">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="4">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="4">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="4">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="4">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="4">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="4">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="4">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="4">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="4">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="4">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="4">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="4">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="4">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="4">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="4">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="4">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="4">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="4">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="4">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="4">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/aysha/FittingTests.xlsx
+++ b/aysha/FittingTests.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\transp02\d$\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\transp02.cheng.auth.gr\d$\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BC73FE-D035-4640-9039-D2CA19D5ADD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE2A4D5-BBC3-42B5-8464-16B9789FF2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
